--- a/ONCHO/Impact Assessments/Eq Guinea/gq_oncho_bsa_2507_3_river_nuis.xlsx
+++ b/ONCHO/Impact Assessments/Eq Guinea/gq_oncho_bsa_2507_3_river_nuis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Impact Assessments\Eq Guinea\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2EEC68-1AE0-4E3A-BD4E-52D25E8A9947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F15A873-3DDA-41EE-9605-3AE6FF65557E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -694,9 +694,6 @@
     <t>s_barecode_id</t>
   </si>
   <si>
-    <t>if(${p_id_type} = 'Escáner', concat(${s_barecode_id}), concat(${s_manual_id}))</t>
-  </si>
-  <si>
     <t>sex</t>
   </si>
   <si>
@@ -968,6 +965,9 @@
   </si>
   <si>
     <t>gq_oncho_bsa_2507_3_river_nuis</t>
+  </si>
+  <si>
+    <t>if(${p_id_type} = 'Escáner', concat(${s_barecode_id}), concat(${s_site_id}, '_', ${s_manual_id}))</t>
   </si>
 </sst>
 </file>
@@ -1692,7 +1692,7 @@
         <v>85</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E1" s="15" t="s">
         <v>2</v>
@@ -1707,7 +1707,7 @@
         <v>5</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J1" s="15" t="s">
         <v>6</v>
@@ -1978,11 +1978,11 @@
         <v>197</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F12" s="35"/>
       <c r="G12" s="31"/>
@@ -2095,7 +2095,7 @@
       <c r="I16" s="45"/>
       <c r="J16" s="9"/>
       <c r="K16" s="46" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L16" s="8"/>
       <c r="M16" s="44" t="s">
@@ -2124,7 +2124,7 @@
       <c r="I17" s="45"/>
       <c r="J17" s="9"/>
       <c r="K17" s="46" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L17" s="8"/>
       <c r="M17" s="44" t="s">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K18" s="46"/>
       <c r="L18" s="8" t="s">
-        <v>219</v>
+        <v>310</v>
       </c>
       <c r="M18" s="44"/>
       <c r="N18" s="8"/>
@@ -2168,7 +2168,7 @@
     </row>
     <row r="19" spans="1:15" s="5" customFormat="1">
       <c r="A19" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>180</v>
@@ -2209,7 +2209,7 @@
         <v>34</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C21" s="23" t="s">
         <v>172</v>
@@ -2225,17 +2225,17 @@
     </row>
     <row r="22" spans="1:15" s="5" customFormat="1" ht="63">
       <c r="A22" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>182</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D22" s="23"/>
       <c r="E22" s="19" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F22" s="17"/>
       <c r="I22" s="26"/>
@@ -2247,7 +2247,7 @@
         <v>190</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C23" s="23"/>
       <c r="D23" s="23"/>
@@ -2256,23 +2256,23 @@
       <c r="I23" s="26"/>
       <c r="J23" s="18"/>
       <c r="L23" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O23" s="10"/>
     </row>
     <row r="24" spans="1:15" s="5" customFormat="1" ht="31.5">
       <c r="A24" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>183</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F24" s="17"/>
       <c r="I24" s="26"/>
@@ -2284,7 +2284,7 @@
         <v>190</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C25" s="23"/>
       <c r="D25" s="23"/>
@@ -2293,29 +2293,29 @@
       <c r="I25" s="26"/>
       <c r="J25" s="18"/>
       <c r="L25" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O25" s="10"/>
     </row>
     <row r="26" spans="1:15" s="5" customFormat="1" ht="47.25">
       <c r="A26" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>184</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D26" s="23"/>
       <c r="E26" s="19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F26" s="17"/>
       <c r="I26" s="26"/>
       <c r="J26" s="18"/>
       <c r="K26" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O26" s="10"/>
     </row>
@@ -2324,7 +2324,7 @@
         <v>190</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C27" s="23"/>
       <c r="D27" s="23"/>
@@ -2333,29 +2333,29 @@
       <c r="I27" s="26"/>
       <c r="J27" s="18"/>
       <c r="L27" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O27" s="10"/>
     </row>
     <row r="28" spans="1:15" s="5" customFormat="1" ht="63">
       <c r="A28" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B28" s="10" t="s">
         <v>185</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D28" s="23"/>
       <c r="E28" s="19" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F28" s="17"/>
       <c r="I28" s="26"/>
       <c r="J28" s="18"/>
       <c r="K28" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O28" s="10"/>
     </row>
@@ -2364,7 +2364,7 @@
         <v>190</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C29" s="23"/>
       <c r="D29" s="23"/>
@@ -2373,29 +2373,29 @@
       <c r="I29" s="26"/>
       <c r="J29" s="18"/>
       <c r="L29" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O29" s="10"/>
     </row>
     <row r="30" spans="1:15" s="5" customFormat="1" ht="47.25">
       <c r="A30" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>187</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D30" s="23"/>
       <c r="E30" s="19" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F30" s="17"/>
       <c r="I30" s="26"/>
       <c r="J30" s="18"/>
       <c r="K30" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O30" s="10"/>
     </row>
@@ -2404,7 +2404,7 @@
         <v>190</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
@@ -2413,29 +2413,29 @@
       <c r="I31" s="26"/>
       <c r="J31" s="18"/>
       <c r="L31" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O31" s="10"/>
     </row>
     <row r="32" spans="1:15" s="5" customFormat="1" ht="63">
       <c r="A32" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>186</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D32" s="23"/>
       <c r="E32" s="19" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F32" s="17"/>
       <c r="I32" s="26"/>
       <c r="J32" s="18"/>
       <c r="K32" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O32" s="10"/>
     </row>
@@ -2444,7 +2444,7 @@
         <v>190</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C33" s="23"/>
       <c r="D33" s="23"/>
@@ -2453,29 +2453,29 @@
       <c r="I33" s="26"/>
       <c r="J33" s="18"/>
       <c r="L33" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O33" s="10"/>
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="63">
       <c r="A34" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>188</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D34" s="23"/>
       <c r="E34" s="19" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F34" s="17"/>
       <c r="I34" s="26"/>
       <c r="J34" s="18"/>
       <c r="K34" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O34" s="10"/>
     </row>
@@ -2484,7 +2484,7 @@
         <v>190</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C35" s="23"/>
       <c r="D35" s="23"/>
@@ -2493,29 +2493,29 @@
       <c r="I35" s="26"/>
       <c r="J35" s="18"/>
       <c r="L35" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O35" s="10"/>
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="78.75">
       <c r="A36" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D36" s="23"/>
       <c r="E36" s="19" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F36" s="17"/>
       <c r="I36" s="26"/>
       <c r="J36" s="18"/>
       <c r="K36" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O36" s="10"/>
     </row>
@@ -2524,7 +2524,7 @@
         <v>190</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C37" s="23"/>
       <c r="D37" s="23"/>
@@ -2533,7 +2533,7 @@
       <c r="I37" s="26"/>
       <c r="J37" s="18"/>
       <c r="L37" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O37" s="10"/>
     </row>
@@ -2545,17 +2545,17 @@
         <v>189</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D38" s="23"/>
       <c r="E38" s="19" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F38" s="17"/>
       <c r="I38" s="26"/>
       <c r="J38" s="18"/>
       <c r="K38" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O38" s="10"/>
     </row>
@@ -2564,7 +2564,7 @@
         <v>190</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C39" s="23"/>
       <c r="D39" s="23"/>
@@ -2573,7 +2573,7 @@
       <c r="I39" s="26"/>
       <c r="J39" s="18"/>
       <c r="L39" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O39" s="10"/>
     </row>
@@ -2582,7 +2582,7 @@
         <v>190</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C40" s="23"/>
       <c r="D40" s="23"/>
@@ -2591,23 +2591,23 @@
       <c r="I40" s="26"/>
       <c r="J40" s="18"/>
       <c r="L40" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O40" s="10"/>
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="31.5">
       <c r="A41" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B41" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="B41" s="10" t="s">
-        <v>307</v>
-      </c>
       <c r="C41" s="23" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D41" s="23"/>
       <c r="E41" s="19" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F41" s="17"/>
       <c r="I41" s="26"/>
@@ -2644,7 +2644,7 @@
     </row>
     <row r="43" spans="1:17" s="1" customFormat="1">
       <c r="A43" s="59" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B43" s="32"/>
       <c r="C43" s="33"/>
@@ -3146,16 +3146,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="C28" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>221</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>222</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -3163,16 +3163,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B29" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>223</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>224</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
@@ -3180,16 +3180,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="58" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B30" s="58" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C30" s="58" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D30" s="58" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
@@ -3197,16 +3197,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="58" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B31" s="58" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C31" s="58" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D31" s="58" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="58" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B32" s="58" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C32" s="58" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D32" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
@@ -3231,16 +3231,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="58" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B33" s="58" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C33" s="58" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D33" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
@@ -3248,16 +3248,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="58" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B34" s="58" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C34" s="58" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D34" s="58" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
@@ -3265,16 +3265,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="58" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B35" s="58" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C35" s="58" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D35" s="58" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
@@ -3282,16 +3282,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="58" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B36" s="58" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C36" s="58" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D36" s="58" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
@@ -3299,16 +3299,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="58" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B37" s="58" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C37" s="58" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D37" s="58" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
@@ -3316,16 +3316,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="58" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C38" s="58" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D38" s="58" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
@@ -3333,16 +3333,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="58" t="s">
+        <v>254</v>
+      </c>
+      <c r="B39" s="58" t="s">
+        <v>257</v>
+      </c>
+      <c r="C39" s="58" t="s">
+        <v>257</v>
+      </c>
+      <c r="D39" s="58" t="s">
         <v>255</v>
-      </c>
-      <c r="B39" s="58" t="s">
-        <v>258</v>
-      </c>
-      <c r="C39" s="58" t="s">
-        <v>258</v>
-      </c>
-      <c r="D39" s="58" t="s">
-        <v>256</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
@@ -3350,16 +3350,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="58" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B40" s="58" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C40" s="58" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D40" s="58" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
@@ -3367,16 +3367,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="58" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B41" s="58" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C41" s="58" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D41" s="58" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
@@ -3384,16 +3384,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="58" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B42" s="58" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C42" s="58" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D42" s="58" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
@@ -4969,7 +4969,7 @@
         <v>83</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4977,7 +4977,7 @@
         <v>153</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>84</v>
